--- a/astro-site/public/dl/plan-negocio-panaderia/plan-financiero-panaderia.xlsx
+++ b/astro-site/public/dl/plan-negocio-panaderia/plan-financiero-panaderia.xlsx
@@ -1539,7 +1539,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
         <v>0.025479404463681774</v>
       </c>
       <c r="D28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico + certificación, Obra civil y adecuación local, Instalación eléctrica (potencia 30-40 kW), Salida humos + ventilación obrador y Rotulación + imagen exterior), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico + certificación, Obra civil y adecuación local, Instalación eléctrica (potencia 30-40 kW), Salida humos + ventilación obrador y Rotulación + imagen exterior), no "&amp;"del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
         <v>Al 10% de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico + certificación, Obra civil y adecuación local, Instalación eléctrica (potencia 30-40 kW), Salida humos + ventilación obrador y Rotulación + imagen exterior), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E28" s="33" t="inlineStr">
@@ -2305,7 +2305,7 @@
         <v>19593.0</v>
       </c>
       <c r="D33" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
         <v>9292.222222222223</v>
       </c>
       <c r="D38" s="37" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución SL + notaría, Licencia actividad (clasificada), Marketing lanzamiento, Stock inicial (harinas, levaduras, etc.), Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B31-B36-B37,"0")&amp;" € de los "&amp;TEXT(B31,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución SL + notaría, Licencia actividad (clasificada), Marketing lanzamiento, Stock inicial (harinas, levaduras, etc.), Fianza del alquiler, Alquiler de los meses previos a la apertura ni "&amp;"Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B31-B36-B37,"0")&amp;" € de los "&amp;TEXT(B31,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Constitución SL + notaría, Licencia actividad (clasificada), Marketing lanzamiento, Stock inicial (harinas, levaduras, etc.), Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman 57515 € de los 145215 € de inversión.</v>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>0.26825</v>
       </c>
       <c r="F13" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$13,"0%")&amp;" de las ventas de COMIDA, no del total: la bebida tiene su propia línea · El IVA que SOPORTAS al comprar es el ponderado de las harinas panificables al 4 % (art. 91.Dos.1.1.º de la Ley 37/1992) y del resto de la materia prima al 10 %, con el mismo peso de pan común que declara la línea de ventas de arriba","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$13,"0%")&amp;" de las ventas de COMIDA, no del total: la bebida tiene su propia línea · El IVA que SOPORTAS al comprar es el ponderado de las harinas panificables al 4 % (art. 91.Dos.1.1.º de la Ley 37/1992) y del resto de la materia prima al 10 %, con "&amp;"el mismo peso de pan común que declara la línea de ventas de arriba","")</f>
         <v>Al 29% de las ventas de COMIDA, no del total: la bebida tiene su propia línea · El IVA que SOPORTAS al comprar es el ponderado de las harinas panificables al 4 % (art. 91.Dos.1.1.º de la Ley 37/1992) y del resto de la materia prima al 10 %, con el mismo peso de pan común que declara la línea de ventas de arriba</v>
       </c>
       <c r="G13" s="30">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F24" s="28" t="n"/>

--- a/astro-site/public/dl/plan-negocio-panaderia/plan-financiero-panaderia.xlsx
+++ b/astro-site/public/dl/plan-negocio-panaderia/plan-financiero-panaderia.xlsx
@@ -1539,7 +1539,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-panaderia/plan-financiero-panaderia.xlsx
+++ b/astro-site/public/dl/plan-negocio-panaderia/plan-financiero-panaderia.xlsx
@@ -1539,7 +1539,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
         <v>0.025479404463681774</v>
       </c>
       <c r="D28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico + certificación, Obra civil y adecuación local, Instalación eléctrica (potencia 30-40 kW), Salida humos + ventilación obrador y Rotulación + imagen exterior), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico + certificación, Obra civil y adecuación local, Instalación eléctrica (potencia 30-40 kW), Salida humos + ventilación obrador y Rotulación + imagen exterior), no "&amp;"del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
         <v>Al 10% de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico + certificación, Obra civil y adecuación local, Instalación eléctrica (potencia 30-40 kW), Salida humos + ventilación obrador y Rotulación + imagen exterior), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E28" s="33" t="inlineStr">
@@ -2305,7 +2305,7 @@
         <v>19593.0</v>
       </c>
       <c r="D33" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
         <v>9292.222222222223</v>
       </c>
       <c r="D38" s="37" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución SL + notaría, Licencia actividad (clasificada), Marketing lanzamiento, Stock inicial (harinas, levaduras, etc.), Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B31-B36-B37,"0")&amp;" € de los "&amp;TEXT(B31,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Constitución SL + notaría, Licencia actividad (clasificada), Marketing lanzamiento, Stock inicial (harinas, levaduras, etc.), Fianza del alquiler, Alquiler de los meses previos a la apertura ni "&amp;"Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B31-B36-B37,"0")&amp;" € de los "&amp;TEXT(B31,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Constitución SL + notaría, Licencia actividad (clasificada), Marketing lanzamiento, Stock inicial (harinas, levaduras, etc.), Fianza del alquiler, Alquiler de los meses previos a la apertura ni Colchón operativo hasta alcanzar el equilibrio. Suman 57515 € de los 145215 € de inversión.</v>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>0.26825</v>
       </c>
       <c r="F13" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$13,"0%")&amp;" de las ventas de COMIDA, no del total: la bebida tiene su propia línea · El IVA que SOPORTAS al comprar es el ponderado de las harinas panificables al 4 % (art. 91.Dos.1.1.º de la Ley 37/1992) y del resto de la materia prima al 10 %, con el mismo peso de pan común que declara la línea de ventas de arriba","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$13,"0%")&amp;" de las ventas de COMIDA, no del total: la bebida tiene su propia línea · El IVA que SOPORTAS al comprar es el ponderado de las harinas panificables al 4 % (art. 91.Dos.1.1.º de la Ley 37/1992) y del resto de la materia prima al 10 %, con "&amp;"el mismo peso de pan común que declara la línea de ventas de arriba","")</f>
         <v>Al 29% de las ventas de COMIDA, no del total: la bebida tiene su propia línea · El IVA que SOPORTAS al comprar es el ponderado de las harinas panificables al 4 % (art. 91.Dos.1.1.º de la Ley 37/1992) y del resto de la materia prima al 10 %, con el mismo peso de pan común que declara la línea de ventas de arriba</v>
       </c>
       <c r="G13" s="30">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F24" s="28" t="n"/>
